--- a/output/pdf_financials_xlsx/SPB.xlsx
+++ b/output/pdf_financials_xlsx/SPB.xlsx
@@ -2194,10 +2194,10 @@
         <v>0</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>31.8</v>
       </c>
       <c r="I34" s="1" t="inlineStr">
         <is>
@@ -2288,10 +2288,10 @@
         <v>0</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>31.8</v>
       </c>
       <c r="I36" s="1" t="inlineStr">
         <is>
@@ -2852,10 +2852,10 @@
         <v>62.9</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>72.8</v>
+        <v>67.8</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>106</v>
+        <v>74.2</v>
       </c>
       <c r="I48" s="1" t="inlineStr">
         <is>
@@ -17832,7 +17832,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -20208,7 +20208,7 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">

--- a/output/pdf_financials_xlsx/SPB.xlsx
+++ b/output/pdf_financials_xlsx/SPB.xlsx
@@ -5284,16 +5284,16 @@
         </is>
       </c>
       <c r="E100" s="3" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="I100" s="1" t="inlineStr">
         <is>
@@ -5813,10 +5813,10 @@
         </is>
       </c>
       <c r="B112" s="3" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="C112" s="3" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="D112" s="1" t="inlineStr">
         <is>
@@ -50020,7 +50020,7 @@
       </c>
       <c r="D657" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E657" t="inlineStr">
@@ -52176,7 +52176,7 @@
       </c>
       <c r="D690" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E690" t="inlineStr">
@@ -56488,7 +56488,7 @@
       </c>
       <c r="D756" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E756" t="inlineStr">
@@ -58850,7 +58850,11 @@
           <t>Proceeds on disposal of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D792" t="inlineStr"/>
+      <c r="D792" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E792" s="5" t="n">
         <v>4.8</v>
       </c>
